--- a/data/availability/projects/mountain-view/lvls.xlsx
+++ b/data/availability/projects/mountain-view/lvls.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Template for LVLS</t>
+          <t>Live inventory for lvls</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,156 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>payment_plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>lvls</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>145</v>
+      </c>
+      <c r="F2" t="n">
+        <v>145</v>
+      </c>
+      <c r="G2" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="H2" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Phase-1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lvls</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>185</v>
+      </c>
+      <c r="F3" t="n">
+        <v>185</v>
+      </c>
+      <c r="G3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H3" t="n">
+        <v>36</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Phase-2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>lvls</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>180</v>
+      </c>
+      <c r="F4" t="n">
+        <v>185</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="H4" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Phase-1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
         </is>
       </c>
     </row>
@@ -557,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +774,250 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>lvls</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LV-BT-BH-377-14</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Phase-1</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>145</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>| Roof: 62 sqm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Corner</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>21469929</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lvls</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LV-SM-TH-143-D</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Phase-2</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>185</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>| Roof: 15 sqm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>35999106</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>lvls</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LV-SM-TH-181-B</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Phase-1</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>180</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>| Roof: 15 sqm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Middle</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>37700941</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lvls</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LV-SM-TH-230-A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Phase-1</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>185</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>| Roof: 15 sqm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Corner</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>28937945</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>

--- a/data/availability/projects/mountain-view/lvls.xlsx
+++ b/data/availability/projects/mountain-view/lvls.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for lvls</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -759,7 +769,6 @@
       <c r="G2" t="n">
         <v>122</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -770,7 +779,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -816,7 +825,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -827,7 +835,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -873,7 +881,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -884,7 +891,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -930,7 +937,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -941,7 +947,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -987,7 +993,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -998,7 +1003,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1044,7 +1049,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1055,7 +1059,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1105,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1112,7 +1115,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1158,7 +1161,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1169,7 +1171,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">

--- a/data/availability/projects/mountain-view/lvls.xlsx
+++ b/data/availability/projects/mountain-view/lvls.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
